--- a/ig/DM-JUIN-2026/CodeSystem-tre-r365-etat-objet.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-tre-r365-etat-objet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>38</t>
+    <t>40</t>
   </si>
   <si>
     <t>Code</t>
@@ -263,6 +263,18 @@
   </si>
   <si>
     <t>Première autorisation de l'EGE</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>Activité Etablissement Psychiatrique créée</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Activité Etablissement Psychiatrique supprimée</t>
   </si>
   <si>
     <t>010</t>
@@ -900,7 +912,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1373,6 +1385,30 @@
       </c>
       <c r="D39" s="2"/>
     </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="D41" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
